--- a/20250426_Vipers/01_source/Weekly_Barge_Scorecard_20250425.xlsx
+++ b/20250426_Vipers/01_source/Weekly_Barge_Scorecard_20250425.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25831"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usaf-my.dps.mil/personal/jennifer_shelton_4_us_af_mil/Documents/Desktop/Barge Status/Weeklyscorecard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional\04_Git\AI_Power_Studio\20250426_Vipers\01_source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_8B35F6202D72326C0BB207BC427F3CFF5380BD9C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87C2D003-379F-4B16-9467-3D83D96EA8F0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4906AC1-8BE8-4B32-A246-8495614C2FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="30" windowWidth="19420" windowHeight="10160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4670" yWindow="430" windowWidth="31320" windowHeight="20370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="40">
   <si>
     <r>
       <rPr>
@@ -429,10 +429,11 @@
     </r>
   </si>
   <si>
-    <t>AC2</t>
-  </si>
-  <si>
-    <t>AC1</t>
+    <t>Aircraft 1</t>
+  </si>
+  <si>
+    <t>Aircraft 1</t>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -440,9 +441,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/dd/yyyy;@"/>
+    <numFmt numFmtId="176" formatCode="m/dd/yyyy;@"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -520,6 +521,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -549,7 +556,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -682,30 +689,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -720,20 +703,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="54">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" indent="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -745,19 +728,19 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" textRotation="180" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -766,7 +749,7 @@
     <xf numFmtId="1" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="1" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -781,13 +764,43 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -799,25 +812,25 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -853,54 +866,9 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -916,9 +884,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -956,9 +924,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -991,9 +959,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1026,9 +1011,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1205,6 +1207,7 @@
   <dimension ref="A1:X22"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="21.59765625" customWidth="1"/>
     <col min="2" max="2" width="16.19921875" customWidth="1"/>
     <col min="3" max="3" width="6.8984375" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
@@ -1227,58 +1230,58 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="23"/>
-      <c r="S1" s="24"/>
-      <c r="T1" s="24"/>
-      <c r="U1" s="24"/>
-      <c r="V1" s="24"/>
-      <c r="W1" s="24"/>
-      <c r="X1" s="25"/>
+      <c r="C1" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="35"/>
     </row>
     <row r="2" spans="1:24" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4">
         <v>45768</v>
       </c>
-      <c r="C2" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="29" t="s">
+      <c r="C2" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="30"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="33" t="s">
+      <c r="H2" s="40"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="34"/>
+      <c r="L2" s="44"/>
       <c r="M2" s="5"/>
-      <c r="N2" s="35" t="s">
+      <c r="N2" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="37"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="47"/>
       <c r="R2" s="6" t="s">
         <v>6</v>
       </c>
@@ -1435,36 +1438,36 @@
     </row>
     <row r="5" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="12"/>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="40"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="50"/>
       <c r="J5" s="12"/>
-      <c r="K5" s="41" t="s">
+      <c r="K5" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="42"/>
-      <c r="M5" s="42"/>
-      <c r="N5" s="42"/>
-      <c r="O5" s="42"/>
-      <c r="P5" s="42"/>
-      <c r="Q5" s="42"/>
-      <c r="R5" s="42"/>
-      <c r="S5" s="42"/>
-      <c r="T5" s="42"/>
-      <c r="U5" s="42"/>
-      <c r="V5" s="42"/>
-      <c r="W5" s="42"/>
-      <c r="X5" s="43"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="52"/>
+      <c r="N5" s="52"/>
+      <c r="O5" s="52"/>
+      <c r="P5" s="52"/>
+      <c r="Q5" s="52"/>
+      <c r="R5" s="52"/>
+      <c r="S5" s="52"/>
+      <c r="T5" s="52"/>
+      <c r="U5" s="52"/>
+      <c r="V5" s="52"/>
+      <c r="W5" s="52"/>
+      <c r="X5" s="53"/>
     </row>
     <row r="6" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="52"/>
-      <c r="B6" s="44" t="s">
+      <c r="A6" s="22"/>
+      <c r="B6" s="20" t="s">
         <v>26</v>
       </c>
       <c r="C6" s="11">
@@ -1527,10 +1530,10 @@
       <c r="X6" s="12"/>
     </row>
     <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="46" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="45" t="s">
+      <c r="A7" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="21" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="15">
@@ -1591,8 +1594,10 @@
       <c r="X7" s="12"/>
     </row>
     <row r="8" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="47"/>
-      <c r="B8" s="45" t="s">
+      <c r="A8" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="21" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="15">
@@ -1651,8 +1656,10 @@
       <c r="X8" s="12"/>
     </row>
     <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="47"/>
-      <c r="B9" s="45" t="s">
+      <c r="A9" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="21" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="15">
@@ -1713,8 +1720,10 @@
       <c r="X9" s="12"/>
     </row>
     <row r="10" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="47"/>
-      <c r="B10" s="45" t="s">
+      <c r="A10" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="21" t="s">
         <v>31</v>
       </c>
       <c r="C10" s="15">
@@ -1771,8 +1780,10 @@
       <c r="X10" s="12"/>
     </row>
     <row r="11" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47"/>
-      <c r="B11" s="45" t="s">
+      <c r="A11" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="21" t="s">
         <v>32</v>
       </c>
       <c r="C11" s="15">
@@ -1829,8 +1840,10 @@
       <c r="X11" s="12"/>
     </row>
     <row r="12" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="47"/>
-      <c r="B12" s="45" t="s">
+      <c r="A12" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="21" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="15">
@@ -1885,8 +1898,10 @@
       <c r="X12" s="12"/>
     </row>
     <row r="13" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="48"/>
-      <c r="B13" s="45" t="s">
+      <c r="A13" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="21" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="12"/>
@@ -1917,40 +1932,40 @@
       <c r="X13" s="12"/>
     </row>
     <row r="14" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="56"/>
-      <c r="C14" s="38" t="s">
+      <c r="B14" s="25"/>
+      <c r="C14" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="40"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="50"/>
       <c r="J14" s="12"/>
-      <c r="K14" s="41" t="s">
+      <c r="K14" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="L14" s="42"/>
-      <c r="M14" s="42"/>
-      <c r="N14" s="42"/>
-      <c r="O14" s="42"/>
-      <c r="P14" s="42"/>
-      <c r="Q14" s="42"/>
-      <c r="R14" s="42"/>
-      <c r="S14" s="42"/>
-      <c r="T14" s="42"/>
-      <c r="U14" s="42"/>
-      <c r="V14" s="42"/>
-      <c r="W14" s="42"/>
-      <c r="X14" s="43"/>
+      <c r="L14" s="52"/>
+      <c r="M14" s="52"/>
+      <c r="N14" s="52"/>
+      <c r="O14" s="52"/>
+      <c r="P14" s="52"/>
+      <c r="Q14" s="52"/>
+      <c r="R14" s="52"/>
+      <c r="S14" s="52"/>
+      <c r="T14" s="52"/>
+      <c r="U14" s="52"/>
+      <c r="V14" s="52"/>
+      <c r="W14" s="52"/>
+      <c r="X14" s="53"/>
     </row>
     <row r="15" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="53"/>
-      <c r="B15" s="58" t="s">
+      <c r="A15" s="23"/>
+      <c r="B15" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="55">
+      <c r="C15" s="24">
         <v>97</v>
       </c>
       <c r="D15" s="11">
@@ -2012,10 +2027,10 @@
       <c r="X15" s="12"/>
     </row>
     <row r="16" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="54" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="57" t="s">
+      <c r="A16" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="26" t="s">
         <v>28</v>
       </c>
       <c r="C16" s="15">
@@ -2076,8 +2091,10 @@
       <c r="X16" s="12"/>
     </row>
     <row r="17" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="50"/>
-      <c r="B17" s="45" t="s">
+      <c r="A17" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="21" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="15">
@@ -2136,8 +2153,10 @@
       <c r="X17" s="12"/>
     </row>
     <row r="18" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="50"/>
-      <c r="B18" s="45" t="s">
+      <c r="A18" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="21" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="15">
@@ -2198,8 +2217,10 @@
       <c r="X18" s="12"/>
     </row>
     <row r="19" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="50"/>
-      <c r="B19" s="45" t="s">
+      <c r="A19" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="21" t="s">
         <v>31</v>
       </c>
       <c r="C19" s="15">
@@ -2256,8 +2277,10 @@
       <c r="X19" s="12"/>
     </row>
     <row r="20" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="50"/>
-      <c r="B20" s="45" t="s">
+      <c r="A20" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="21" t="s">
         <v>32</v>
       </c>
       <c r="C20" s="15">
@@ -2314,8 +2337,10 @@
       <c r="X20" s="12"/>
     </row>
     <row r="21" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="50"/>
-      <c r="B21" s="45" t="s">
+      <c r="A21" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="21" t="s">
         <v>33</v>
       </c>
       <c r="C21" s="15">
@@ -2374,8 +2399,10 @@
       <c r="X21" s="12"/>
     </row>
     <row r="22" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="51"/>
-      <c r="B22" s="45" t="s">
+      <c r="A22" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="21" t="s">
         <v>34</v>
       </c>
       <c r="C22" s="12"/>
@@ -2406,13 +2433,7 @@
       <c r="X22" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="K14:X14"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="A16:A22"/>
+  <mergeCells count="11">
     <mergeCell ref="C1:Q1"/>
     <mergeCell ref="R1:X1"/>
     <mergeCell ref="C2:F2"/>
@@ -2420,8 +2441,14 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="N2:Q2"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="K14:X14"/>
   </mergeCells>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2452,58 +2479,58 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="23"/>
-      <c r="S1" s="24"/>
-      <c r="T1" s="24"/>
-      <c r="U1" s="24"/>
-      <c r="V1" s="24"/>
-      <c r="W1" s="24"/>
-      <c r="X1" s="25"/>
+      <c r="C1" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="35"/>
     </row>
     <row r="2" spans="1:24" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4">
         <v>45768</v>
       </c>
-      <c r="C2" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="29" t="s">
+      <c r="C2" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="30"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="33" t="s">
+      <c r="H2" s="40"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="34"/>
+      <c r="L2" s="44"/>
       <c r="M2" s="5"/>
-      <c r="N2" s="35" t="s">
+      <c r="N2" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="37"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="47"/>
       <c r="R2" s="6" t="s">
         <v>6</v>
       </c>
@@ -2660,39 +2687,39 @@
     </row>
     <row r="5" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="12"/>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="40"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="50"/>
       <c r="J5" s="12"/>
-      <c r="K5" s="41" t="s">
+      <c r="K5" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="42"/>
-      <c r="M5" s="42"/>
-      <c r="N5" s="42"/>
-      <c r="O5" s="42"/>
-      <c r="P5" s="42"/>
-      <c r="Q5" s="42"/>
-      <c r="R5" s="42"/>
-      <c r="S5" s="42"/>
-      <c r="T5" s="42"/>
-      <c r="U5" s="42"/>
-      <c r="V5" s="42"/>
-      <c r="W5" s="42"/>
-      <c r="X5" s="43"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="52"/>
+      <c r="N5" s="52"/>
+      <c r="O5" s="52"/>
+      <c r="P5" s="52"/>
+      <c r="Q5" s="52"/>
+      <c r="R5" s="52"/>
+      <c r="S5" s="52"/>
+      <c r="T5" s="52"/>
+      <c r="U5" s="52"/>
+      <c r="V5" s="52"/>
+      <c r="W5" s="52"/>
+      <c r="X5" s="53"/>
     </row>
     <row r="6" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="29" t="s">
         <v>39</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>26</v>
       </c>
       <c r="C6" s="11">
         <v>93</v>
@@ -2754,8 +2781,10 @@
       <c r="X6" s="12"/>
     </row>
     <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="47"/>
-      <c r="B7" s="45" t="s">
+      <c r="A7" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="21" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="15">
@@ -2816,8 +2845,10 @@
       <c r="X7" s="12"/>
     </row>
     <row r="8" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="47"/>
-      <c r="B8" s="45" t="s">
+      <c r="A8" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="21" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="15">
@@ -2876,8 +2907,10 @@
       <c r="X8" s="12"/>
     </row>
     <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="47"/>
-      <c r="B9" s="45" t="s">
+      <c r="A9" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="21" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="15">
@@ -2938,8 +2971,10 @@
       <c r="X9" s="12"/>
     </row>
     <row r="10" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="47"/>
-      <c r="B10" s="45" t="s">
+      <c r="A10" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="21" t="s">
         <v>31</v>
       </c>
       <c r="C10" s="15">
@@ -2996,8 +3031,10 @@
       <c r="X10" s="12"/>
     </row>
     <row r="11" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47"/>
-      <c r="B11" s="45" t="s">
+      <c r="A11" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="21" t="s">
         <v>32</v>
       </c>
       <c r="C11" s="15">
@@ -3054,8 +3091,10 @@
       <c r="X11" s="12"/>
     </row>
     <row r="12" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="47"/>
-      <c r="B12" s="45" t="s">
+      <c r="A12" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="21" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="15">
@@ -3110,8 +3149,10 @@
       <c r="X12" s="12"/>
     </row>
     <row r="13" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="48"/>
-      <c r="B13" s="45" t="s">
+      <c r="A13" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="21" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="12"/>
@@ -3143,38 +3184,38 @@
     </row>
     <row r="14" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="12"/>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="40"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="50"/>
       <c r="J14" s="12"/>
-      <c r="K14" s="41" t="s">
+      <c r="K14" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="L14" s="42"/>
-      <c r="M14" s="42"/>
-      <c r="N14" s="42"/>
-      <c r="O14" s="42"/>
-      <c r="P14" s="42"/>
-      <c r="Q14" s="42"/>
-      <c r="R14" s="42"/>
-      <c r="S14" s="42"/>
-      <c r="T14" s="42"/>
-      <c r="U14" s="42"/>
-      <c r="V14" s="42"/>
-      <c r="W14" s="42"/>
-      <c r="X14" s="43"/>
+      <c r="L14" s="52"/>
+      <c r="M14" s="52"/>
+      <c r="N14" s="52"/>
+      <c r="O14" s="52"/>
+      <c r="P14" s="52"/>
+      <c r="Q14" s="52"/>
+      <c r="R14" s="52"/>
+      <c r="S14" s="52"/>
+      <c r="T14" s="52"/>
+      <c r="U14" s="52"/>
+      <c r="V14" s="52"/>
+      <c r="W14" s="52"/>
+      <c r="X14" s="53"/>
     </row>
     <row r="15" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="49" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="44" t="s">
+      <c r="A15" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="20" t="s">
         <v>37</v>
       </c>
       <c r="C15" s="11">
@@ -3239,8 +3280,10 @@
       <c r="X15" s="12"/>
     </row>
     <row r="16" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="50"/>
-      <c r="B16" s="45" t="s">
+      <c r="A16" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="21" t="s">
         <v>28</v>
       </c>
       <c r="C16" s="15">
@@ -3301,8 +3344,10 @@
       <c r="X16" s="12"/>
     </row>
     <row r="17" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="50"/>
-      <c r="B17" s="45" t="s">
+      <c r="A17" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="21" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="15">
@@ -3361,8 +3406,10 @@
       <c r="X17" s="12"/>
     </row>
     <row r="18" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="50"/>
-      <c r="B18" s="45" t="s">
+      <c r="A18" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="21" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="15">
@@ -3423,8 +3470,10 @@
       <c r="X18" s="12"/>
     </row>
     <row r="19" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="50"/>
-      <c r="B19" s="45" t="s">
+      <c r="A19" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="21" t="s">
         <v>31</v>
       </c>
       <c r="C19" s="15">
@@ -3481,8 +3530,10 @@
       <c r="X19" s="12"/>
     </row>
     <row r="20" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="50"/>
-      <c r="B20" s="45" t="s">
+      <c r="A20" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="21" t="s">
         <v>32</v>
       </c>
       <c r="C20" s="15">
@@ -3539,8 +3590,10 @@
       <c r="X20" s="12"/>
     </row>
     <row r="21" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="50"/>
-      <c r="B21" s="45" t="s">
+      <c r="A21" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="21" t="s">
         <v>33</v>
       </c>
       <c r="C21" s="15">
@@ -3599,8 +3652,10 @@
       <c r="X21" s="12"/>
     </row>
     <row r="22" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="51"/>
-      <c r="B22" s="45" t="s">
+      <c r="A22" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="21" t="s">
         <v>34</v>
       </c>
       <c r="C22" s="12"/>
@@ -3631,13 +3686,11 @@
       <c r="X22" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="11">
     <mergeCell ref="C5:I5"/>
     <mergeCell ref="K5:X5"/>
-    <mergeCell ref="A6:A13"/>
     <mergeCell ref="C14:I14"/>
     <mergeCell ref="K14:X14"/>
-    <mergeCell ref="A15:A22"/>
     <mergeCell ref="C1:Q1"/>
     <mergeCell ref="R1:X1"/>
     <mergeCell ref="C2:F2"/>
@@ -3646,6 +3699,7 @@
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="N2:Q2"/>
   </mergeCells>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/20250426_Vipers/01_source/Weekly_Barge_Scorecard_20250425.xlsx
+++ b/20250426_Vipers/01_source/Weekly_Barge_Scorecard_20250425.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional\04_Git\AI_Power_Studio\20250426_Vipers\01_source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4906AC1-8BE8-4B32-A246-8495614C2FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5ADCBB-08BE-405E-BD6E-0ABE3BBE02DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4670" yWindow="430" windowWidth="31320" windowHeight="20370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3780" yWindow="7190" windowWidth="38400" windowHeight="20370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Table 1 (2)" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="Table 1 (2)" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="41">
   <si>
     <r>
       <rPr>
@@ -433,6 +434,10 @@
   </si>
   <si>
     <t>Aircraft 1</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aircraft</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -528,7 +533,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -555,8 +560,20 @@
         <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -699,11 +716,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -865,6 +895,39 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" textRotation="180" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1243,10 +1306,10 @@
       <c r="K1" s="31"/>
       <c r="L1" s="31"/>
       <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="32"/>
+      <c r="N1" s="58"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="59"/>
       <c r="R1" s="33"/>
       <c r="S1" s="34"/>
       <c r="T1" s="34"/>
@@ -1275,14 +1338,14 @@
         <v>4</v>
       </c>
       <c r="L2" s="44"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="45" t="s">
+      <c r="M2" s="54"/>
+      <c r="N2" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="6" t="s">
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62"/>
+      <c r="R2" s="56" t="s">
         <v>6</v>
       </c>
       <c r="S2" s="6" t="s">
@@ -1336,22 +1399,22 @@
       <c r="L3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="M3" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O3" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="P3" s="9" t="s">
+      <c r="P3" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="Q3" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="R3" s="57" t="s">
         <v>22</v>
       </c>
       <c r="S3" s="9" t="s">
@@ -1406,16 +1469,16 @@
       <c r="M4" s="11">
         <v>55</v>
       </c>
-      <c r="N4" s="11">
+      <c r="N4" s="60">
         <v>9222</v>
       </c>
-      <c r="O4" s="13">
+      <c r="O4" s="61">
         <v>144</v>
       </c>
-      <c r="P4" s="11">
+      <c r="P4" s="60">
         <v>122</v>
       </c>
-      <c r="Q4" s="11">
+      <c r="Q4" s="60">
         <v>103</v>
       </c>
       <c r="R4" s="11">
@@ -1466,7 +1529,9 @@
       <c r="X5" s="53"/>
     </row>
     <row r="6" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
+      <c r="A6" s="22" t="s">
+        <v>40</v>
+      </c>
       <c r="B6" s="20" t="s">
         <v>26</v>
       </c>
@@ -2434,6 +2499,10 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="K14:X14"/>
     <mergeCell ref="C1:Q1"/>
     <mergeCell ref="R1:X1"/>
     <mergeCell ref="C2:F2"/>
@@ -2441,10 +2510,6 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="N2:Q2"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="K14:X14"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2453,6 +2518,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE576F54-3AFC-4CD7-B9C0-37E03AFF29F1}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="13" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFCDD3A4-509C-4C18-9A60-C039068C97D4}">
   <dimension ref="A1:X22"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>

--- a/20250426_Vipers/01_source/Weekly_Barge_Scorecard_20250425.xlsx
+++ b/20250426_Vipers/01_source/Weekly_Barge_Scorecard_20250425.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional\04_Git\AI_Power_Studio\20250426_Vipers\01_source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\AI_Power_Studio\20250426_Vipers\01_source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5ADCBB-08BE-405E-BD6E-0ABE3BBE02DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041EB2FD-6FD9-4C20-AA9C-F01BA6A7DDE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3780" yWindow="7190" windowWidth="38400" windowHeight="20370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5290" yWindow="4930" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
@@ -824,51 +824,102 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -877,57 +928,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="180" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -947,9 +947,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -987,9 +987,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1022,26 +1022,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1074,26 +1057,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1293,59 +1259,59 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="59"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="35"/>
+      <c r="C1" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="50"/>
     </row>
     <row r="2" spans="1:24" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4">
         <v>45768</v>
       </c>
-      <c r="C2" s="36" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="39" t="s">
+      <c r="C2" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="40"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="43" t="s">
+      <c r="H2" s="55"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="44"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="62" t="s">
+      <c r="L2" s="59"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="56" t="s">
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="32" t="s">
         <v>6</v>
       </c>
       <c r="S2" s="6" t="s">
@@ -1399,22 +1365,22 @@
       <c r="L3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="55" t="s">
+      <c r="M3" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="63" t="s">
+      <c r="N3" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="64" t="s">
+      <c r="O3" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="P3" s="64" t="s">
+      <c r="P3" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="64" t="s">
+      <c r="Q3" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="57" t="s">
+      <c r="R3" s="33" t="s">
         <v>22</v>
       </c>
       <c r="S3" s="9" t="s">
@@ -1469,16 +1435,16 @@
       <c r="M4" s="11">
         <v>55</v>
       </c>
-      <c r="N4" s="60">
+      <c r="N4" s="34">
         <v>9222</v>
       </c>
-      <c r="O4" s="61">
+      <c r="O4" s="35">
         <v>144</v>
       </c>
-      <c r="P4" s="60">
+      <c r="P4" s="34">
         <v>122</v>
       </c>
-      <c r="Q4" s="60">
+      <c r="Q4" s="34">
         <v>103</v>
       </c>
       <c r="R4" s="11">
@@ -1501,32 +1467,32 @@
     </row>
     <row r="5" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="12"/>
-      <c r="C5" s="48" t="s">
+      <c r="C5" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="50"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="40"/>
       <c r="J5" s="12"/>
-      <c r="K5" s="51" t="s">
+      <c r="K5" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="52"/>
-      <c r="P5" s="52"/>
-      <c r="Q5" s="52"/>
-      <c r="R5" s="52"/>
-      <c r="S5" s="52"/>
-      <c r="T5" s="52"/>
-      <c r="U5" s="52"/>
-      <c r="V5" s="52"/>
-      <c r="W5" s="52"/>
-      <c r="X5" s="53"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="42"/>
+      <c r="P5" s="42"/>
+      <c r="Q5" s="42"/>
+      <c r="R5" s="42"/>
+      <c r="S5" s="42"/>
+      <c r="T5" s="42"/>
+      <c r="U5" s="42"/>
+      <c r="V5" s="42"/>
+      <c r="W5" s="42"/>
+      <c r="X5" s="43"/>
     </row>
     <row r="6" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
@@ -1998,32 +1964,32 @@
     </row>
     <row r="14" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="25"/>
-      <c r="C14" s="48" t="s">
+      <c r="C14" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="50"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="40"/>
       <c r="J14" s="12"/>
-      <c r="K14" s="51" t="s">
+      <c r="K14" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="L14" s="52"/>
-      <c r="M14" s="52"/>
-      <c r="N14" s="52"/>
-      <c r="O14" s="52"/>
-      <c r="P14" s="52"/>
-      <c r="Q14" s="52"/>
-      <c r="R14" s="52"/>
-      <c r="S14" s="52"/>
-      <c r="T14" s="52"/>
-      <c r="U14" s="52"/>
-      <c r="V14" s="52"/>
-      <c r="W14" s="52"/>
-      <c r="X14" s="53"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="42"/>
+      <c r="O14" s="42"/>
+      <c r="P14" s="42"/>
+      <c r="Q14" s="42"/>
+      <c r="R14" s="42"/>
+      <c r="S14" s="42"/>
+      <c r="T14" s="42"/>
+      <c r="U14" s="42"/>
+      <c r="V14" s="42"/>
+      <c r="W14" s="42"/>
+      <c r="X14" s="43"/>
     </row>
     <row r="15" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="23"/>
@@ -2554,58 +2520,58 @@
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="35"/>
+      <c r="C1" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
+      <c r="L1" s="45"/>
+      <c r="M1" s="45"/>
+      <c r="N1" s="45"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="50"/>
     </row>
     <row r="2" spans="1:24" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4">
         <v>45768</v>
       </c>
-      <c r="C2" s="36" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="39" t="s">
+      <c r="C2" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="40"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="43" t="s">
+      <c r="H2" s="55"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="44"/>
+      <c r="L2" s="59"/>
       <c r="M2" s="5"/>
-      <c r="N2" s="45" t="s">
+      <c r="N2" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="47"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="64"/>
       <c r="R2" s="6" t="s">
         <v>6</v>
       </c>
@@ -2762,32 +2728,32 @@
     </row>
     <row r="5" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="12"/>
-      <c r="C5" s="48" t="s">
+      <c r="C5" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="50"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="40"/>
       <c r="J5" s="12"/>
-      <c r="K5" s="51" t="s">
+      <c r="K5" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="52"/>
-      <c r="P5" s="52"/>
-      <c r="Q5" s="52"/>
-      <c r="R5" s="52"/>
-      <c r="S5" s="52"/>
-      <c r="T5" s="52"/>
-      <c r="U5" s="52"/>
-      <c r="V5" s="52"/>
-      <c r="W5" s="52"/>
-      <c r="X5" s="53"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="42"/>
+      <c r="P5" s="42"/>
+      <c r="Q5" s="42"/>
+      <c r="R5" s="42"/>
+      <c r="S5" s="42"/>
+      <c r="T5" s="42"/>
+      <c r="U5" s="42"/>
+      <c r="V5" s="42"/>
+      <c r="W5" s="42"/>
+      <c r="X5" s="43"/>
     </row>
     <row r="6" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="28" t="s">
@@ -3259,32 +3225,32 @@
     </row>
     <row r="14" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="12"/>
-      <c r="C14" s="48" t="s">
+      <c r="C14" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="50"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="40"/>
       <c r="J14" s="12"/>
-      <c r="K14" s="51" t="s">
+      <c r="K14" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="L14" s="52"/>
-      <c r="M14" s="52"/>
-      <c r="N14" s="52"/>
-      <c r="O14" s="52"/>
-      <c r="P14" s="52"/>
-      <c r="Q14" s="52"/>
-      <c r="R14" s="52"/>
-      <c r="S14" s="52"/>
-      <c r="T14" s="52"/>
-      <c r="U14" s="52"/>
-      <c r="V14" s="52"/>
-      <c r="W14" s="52"/>
-      <c r="X14" s="53"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="42"/>
+      <c r="O14" s="42"/>
+      <c r="P14" s="42"/>
+      <c r="Q14" s="42"/>
+      <c r="R14" s="42"/>
+      <c r="S14" s="42"/>
+      <c r="T14" s="42"/>
+      <c r="U14" s="42"/>
+      <c r="V14" s="42"/>
+      <c r="W14" s="42"/>
+      <c r="X14" s="43"/>
     </row>
     <row r="15" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="20" t="s">

--- a/20250426_Vipers/01_source/Weekly_Barge_Scorecard_20250425.xlsx
+++ b/20250426_Vipers/01_source/Weekly_Barge_Scorecard_20250425.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\AI_Power_Studio\20250426_Vipers\01_source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041EB2FD-6FD9-4C20-AA9C-F01BA6A7DDE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81C506B-67C2-4BA2-AC47-698DC0A170C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5290" yWindow="4930" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="700" yWindow="4220" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="40">
   <si>
     <r>
       <rPr>
@@ -434,10 +434,6 @@
   </si>
   <si>
     <t>Aircraft 1</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>Aircraft</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -1495,9 +1491,7 @@
       <c r="X5" s="43"/>
     </row>
     <row r="6" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
-        <v>40</v>
-      </c>
+      <c r="A6" s="22"/>
       <c r="B6" s="20" t="s">
         <v>26</v>
       </c>
